--- a/uploads/1A.xlsx
+++ b/uploads/1A.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADRIAN\.cursor-tutor\asistencia-simple\uploads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51BE4E81-1358-4CE9-BBB1-0613818D0385}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75D25567-8E08-4102-878C-39F2DB982EDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -857,7 +857,7 @@
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
       <c r="G5" s="3">
-        <v>902500360</v>
+        <v>987170586</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="15" customHeight="1">
